--- a/FLUJO DE CAJA.xlsx
+++ b/FLUJO DE CAJA.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Leonardo\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DaddyChary\Desktop\Entrega Proyecto SmartPark\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD53C676-C7AC-4F90-B383-5B06E18F13A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80D2E941-3CAA-4DCD-A01F-6A35BCDC9A3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7481359D-2BD7-4B50-91FB-69859FDE6FF8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7481359D-2BD7-4B50-91FB-69859FDE6FF8}"/>
   </bookViews>
   <sheets>
     <sheet name="Flujo de caja conservador " sheetId="7" r:id="rId1"/>
@@ -287,12 +287,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
-    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0;[Red]&quot;$&quot;\-#,##0"/>
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00;[Red]&quot;$&quot;\-#,##0.00"/>
-    <numFmt numFmtId="42" formatCode="_ &quot;$&quot;* #,##0_ ;_ &quot;$&quot;* \-#,##0_ ;_ &quot;$&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="164" formatCode="0.000"/>
-    <numFmt numFmtId="165" formatCode="_ * #,##0.0_ ;_ * \-#,##0.0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0;[Red]&quot;$&quot;\-#,##0"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00;[Red]&quot;$&quot;\-#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="_ &quot;$&quot;* #,##0_ ;_ &quot;$&quot;* \-#,##0_ ;_ &quot;$&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="168" formatCode="0.000"/>
+    <numFmt numFmtId="169" formatCode="_ * #,##0.0_ ;_ * \-#,##0.0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -516,22 +516,22 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="42" fontId="0" fillId="6" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -540,55 +540,55 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="42" fontId="0" fillId="8" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="42" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="8" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="42" fontId="0" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="42" fontId="0" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="42" fontId="0" fillId="4" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="42" fontId="3" fillId="8" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="42" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="42" fontId="8" fillId="8" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="42" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="8" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="8" fillId="8" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="42" fontId="0" fillId="7" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="7" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="6" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="42" fontId="3" fillId="7" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="7" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="42" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="41" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="169" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="8" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -612,16 +612,16 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="5" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="5" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -971,13 +971,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
@@ -995,11 +995,11 @@
       <c r="E2" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="G2" s="44" t="s">
+      <c r="G2" s="43" t="s">
         <v>70</v>
       </c>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="42" t="s">
@@ -1009,12 +1009,12 @@
       <c r="C3" s="42"/>
       <c r="D3" s="42"/>
       <c r="E3" s="17"/>
-      <c r="G3" s="45">
+      <c r="G3" s="44">
         <f>NPV(0.12,C43:E43)+B43</f>
         <v>59497700.458875991</v>
       </c>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="44"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
@@ -1055,20 +1055,20 @@
         <f>C5*1.03*1.03</f>
         <v>49650120</v>
       </c>
-      <c r="G5" s="46" t="s">
+      <c r="G5" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="H5" s="46"/>
-      <c r="I5" s="46"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B6" s="6"/>
-      <c r="G6" s="39">
+      <c r="G6" s="46">
         <f>IRR(B43:E43)</f>
         <v>16742.334067163705</v>
       </c>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
+      <c r="H6" s="46"/>
+      <c r="I6" s="46"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="21" t="s">
@@ -1097,13 +1097,13 @@
         <f>C8*1.03*1.03</f>
         <v>-318270</v>
       </c>
-      <c r="G8" s="40" t="s">
+      <c r="G8" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="H8" s="41"/>
-      <c r="I8" s="41"/>
-      <c r="J8" s="41"/>
-      <c r="K8" s="41"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="40"/>
+      <c r="J8" s="40"/>
+      <c r="K8" s="40"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
@@ -1710,18 +1710,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="G1" s="44" t="s">
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="G1" s="43" t="s">
         <v>70</v>
       </c>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
@@ -1739,12 +1739,12 @@
       <c r="E2" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="G2" s="45">
+      <c r="G2" s="44">
         <f>NPV(0.12,C43,D43,E43)+B43</f>
         <v>100493814.71213312</v>
       </c>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="42" t="s">
@@ -1774,11 +1774,11 @@
         <f>C4*1.03*1.03</f>
         <v>74475180</v>
       </c>
-      <c r="G4" s="46" t="s">
+      <c r="G4" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="H4" s="46"/>
-      <c r="I4" s="46"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="45"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
@@ -1799,12 +1799,12 @@
         <f>C5*1.03*1.03</f>
         <v>74475180</v>
       </c>
-      <c r="G5" s="39">
+      <c r="G5" s="46">
         <f>IRR(B43:E43)</f>
         <v>30933.363688239086</v>
       </c>
-      <c r="H5" s="39"/>
-      <c r="I5" s="39"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="46"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B6" s="6"/>
@@ -1836,13 +1836,13 @@
         <f>C8*1.03*1.03</f>
         <v>-318270</v>
       </c>
-      <c r="G8" s="40" t="s">
+      <c r="G8" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="H8" s="41"/>
-      <c r="I8" s="41"/>
-      <c r="J8" s="41"/>
-      <c r="K8" s="41"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="40"/>
+      <c r="J8" s="40"/>
+      <c r="K8" s="40"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
@@ -2447,13 +2447,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
@@ -2480,11 +2480,11 @@
       <c r="C3" s="42"/>
       <c r="D3" s="42"/>
       <c r="E3" s="17"/>
-      <c r="G3" s="44" t="s">
+      <c r="G3" s="43" t="s">
         <v>70</v>
       </c>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
@@ -2505,12 +2505,12 @@
         <f>C4*1.03*1.03</f>
         <v>86887710</v>
       </c>
-      <c r="G4" s="45">
+      <c r="G4" s="44">
         <f>NPV(0.12,C42:E42)+B42</f>
         <v>120991871.83876164</v>
       </c>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="44"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
@@ -2533,11 +2533,11 @@
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="G6" s="46" t="s">
+      <c r="G6" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="H6" s="46"/>
-      <c r="I6" s="46"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="21" t="s">
@@ -2547,12 +2547,12 @@
       <c r="C7" s="17"/>
       <c r="D7" s="17"/>
       <c r="E7" s="17"/>
-      <c r="G7" s="39">
+      <c r="G7" s="46">
         <f>IRR(B42:E42)</f>
         <v>38028.926181986644</v>
       </c>
-      <c r="H7" s="39"/>
-      <c r="I7" s="39"/>
+      <c r="H7" s="46"/>
+      <c r="I7" s="46"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
@@ -2591,13 +2591,13 @@
         <f>C9*1.03*1.03</f>
         <v>-407385.60000000003</v>
       </c>
-      <c r="G9" s="40" t="s">
+      <c r="G9" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="H9" s="41"/>
-      <c r="I9" s="41"/>
-      <c r="J9" s="41"/>
-      <c r="K9" s="41"/>
+      <c r="H9" s="40"/>
+      <c r="I9" s="40"/>
+      <c r="J9" s="40"/>
+      <c r="K9" s="40"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
